--- a/MR_UKBiobank/BinaryData/Logistic/gMR_res.xlsx
+++ b/MR_UKBiobank/BinaryData/Logistic/gMR_res.xlsx
@@ -135,28 +135,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.4654131298615298</v>
+        <v>-1.298155606359874</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.7682965028446587</v>
+        <v>-1.4838012220889936</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.162529756878401</v>
+        <v>-1.1125099906307545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1545323331546576</v>
+        <v>0.09471715088220384</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4733595218194662E-21</v>
+        <v>9.398409407474964E-43</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23098254597575954</v>
+        <v>0.27303491277261416</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17062339787259898</v>
+        <v>0.22677402949400324</v>
       </c>
       <c r="J2" t="n">
-        <v>0.31269413931893103</v>
+        <v>0.3287328084220524</v>
       </c>
     </row>
   </sheetData>
@@ -207,28 +207,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5333080947801566</v>
+        <v>0.5173213617556149</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3889818668301319</v>
+        <v>0.34911636772623666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6776343227301813</v>
+        <v>0.6855263557849932</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07363583058674729</v>
+        <v>0.08581887450478481</v>
       </c>
       <c r="G2" t="n">
-        <v>4.404623307106774E-13</v>
+        <v>1.6593900698134926E-9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7045618441051134</v>
+        <v>1.6775281350846263</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4754777960009646</v>
+        <v>1.417814168553751</v>
       </c>
       <c r="J2" t="n">
-        <v>1.969213693526246</v>
+        <v>1.984816280169525</v>
       </c>
     </row>
   </sheetData>
@@ -279,28 +279,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5510020199787137</v>
+        <v>0.6043621122746538</v>
       </c>
       <c r="D2" t="n">
-        <v>0.36782024770810806</v>
+        <v>0.37008382203242585</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7341837922493193</v>
+        <v>0.8386404025168817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09346008789316612</v>
+        <v>0.11952973991950402</v>
       </c>
       <c r="G2" t="n">
-        <v>3.733531630704509E-9</v>
+        <v>4.2777080024605673E-7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7349906424413457</v>
+        <v>1.830084448069454</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4445823486466167</v>
+        <v>1.447855971807269</v>
       </c>
       <c r="J2" t="n">
-        <v>2.083780500418815</v>
+        <v>2.313219790007889</v>
       </c>
     </row>
   </sheetData>
@@ -351,28 +351,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.20689218703478277</v>
+        <v>-0.07847977288357223</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.47838758901489886</v>
+        <v>-0.3969115331248824</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06460321494533336</v>
+        <v>0.23995198735773798</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13851806223475313</v>
+        <v>0.16246518379658684</v>
       </c>
       <c r="G2" t="n">
-        <v>0.13527716107862248</v>
+        <v>0.6290560136662451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8131073087721079</v>
+        <v>0.924520760131482</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6197819297549271</v>
+        <v>0.6723935075539913</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0667356756271484</v>
+        <v>1.2711881157559515</v>
       </c>
     </row>
   </sheetData>
@@ -423,28 +423,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.028037395135022437</v>
+        <v>0.06798067929762938</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.11692864848303003</v>
+        <v>-0.024335716904758775</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06085385821298515</v>
+        <v>0.16029707550001754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04535268027959571</v>
+        <v>0.04710020214407559</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5364381592998023</v>
+        <v>0.14893025544019442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9723520048868597</v>
+        <v>1.0703446284689981</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8896486686809278</v>
+        <v>0.9759580091516636</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0627435915902972</v>
+        <v>1.1738595441091422</v>
       </c>
     </row>
   </sheetData>
@@ -495,28 +495,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5240574231601224</v>
+        <v>0.5253929826813609</v>
       </c>
       <c r="D2" t="n">
-        <v>0.39243030736688816</v>
+        <v>0.3714837847044969</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6556845389533565</v>
+        <v>0.6793021806582249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06715669173124195</v>
+        <v>0.0785251010086041</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0212131366391994E-15</v>
+        <v>2.2200722005158022E-11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6888662117289683</v>
+        <v>1.6911232999804924</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4805746765376069</v>
+        <v>1.4498843356078557</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9264608035779196</v>
+        <v>1.9725008026505195</v>
       </c>
     </row>
   </sheetData>
